--- a/Data/Building/Lab.AirPurifier001.xlsx
+++ b/Data/Building/Lab.AirPurifier001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709272928</v>
+        <v>1711866788</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709275972</v>
+        <v>1711869195</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709264338</v>
+        <v>1711942632</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709266729</v>
+        <v>1711945092</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709269003</v>
+        <v>1712032894</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709271739</v>
+        <v>1712035300</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709351292</v>
+        <v>1712120381</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709354107</v>
+        <v>1712122845</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709354584</v>
+        <v>1712203959</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709357162</v>
+        <v>1712206562</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709439511</v>
+        <v>1712290188</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709442084</v>
+        <v>1712292725</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709525453</v>
+        <v>1712552644</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709528002</v>
+        <v>1712554910</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709528492</v>
+        <v>1712636209</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709531720</v>
+        <v>1712638516</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709613923</v>
+        <v>1712722503</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709616567</v>
+        <v>1712724695</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709868051</v>
+        <v>1712809715</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709870231</v>
+        <v>1712811399</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709957037</v>
+        <v>1712893828</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709959843</v>
+        <v>1712896249</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1710046251</v>
+        <v>1712896568</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1710049113</v>
+        <v>1712898985</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1710134039</v>
+        <v>1713154399</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1710136454</v>
+        <v>1713157034</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1710217886</v>
+        <v>1713238959</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710220831</v>
+        <v>1713241311</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710475686</v>
+        <v>1713324442</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710478361</v>
+        <v>1713326279</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710562891</v>
+        <v>1713409803</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710565206</v>
+        <v>1713412119</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710653652</v>
+        <v>1713499349</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710656352</v>
+        <v>1713501256</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710735935</v>
+        <v>1713755167</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710738304</v>
+        <v>1713757291</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710823015</v>
+        <v>1713846901</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710825834</v>
+        <v>1713849384</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1711081183</v>
+        <v>1713929790</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1711084029</v>
+        <v>1713932309</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1711170000</v>
+        <v>1714014180</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1711172661</v>
+        <v>1714016940</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1711252922</v>
+        <v>1714100313</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1711255831</v>
+        <v>1714102868</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,150 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>AirPurifier_Operation</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1711337230</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Lab.AirPurifier001.state: on</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>AirPurifier_Operation</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1711339687</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Lab.AirPurifier001.state: off</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>AirPurifier_Operation</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1711427661</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Lab.AirPurifier001.state: on</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>AirPurifier_Operation</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1711430254</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Lab.AirPurifier001.state: off</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
